--- a/databases/teste_dunn_clusters_ans_final_kmeans3.xlsx
+++ b/databases/teste_dunn_clusters_ans_final_kmeans3.xlsx
@@ -399,16 +399,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1: lowest unsafe abortion rates</t>
+          <t>1: lowest induced abortion rates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2: intermediary unsafe abortion rates</t>
+          <t>2: intermediary induced abortion rates</t>
         </is>
       </c>
       <c r="D2">
-        <v>54.01244986775444</v>
+        <v>53.78277875760732</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="G2">
-        <v>-3.583899078061028</v>
+        <v>-3.5886325540013</v>
       </c>
     </row>
     <row r="3">
@@ -430,16 +430,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1: lowest unsafe abortion rates</t>
+          <t>1: lowest induced abortion rates</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3: highest unsafe abortion rates</t>
+          <t>3: highest induced abortion rates</t>
         </is>
       </c>
       <c r="D3">
-        <v>42.26510307378413</v>
+        <v>42.07660716175877</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>-4.174048900886381</v>
+        <v>-4.084776958137041</v>
       </c>
     </row>
     <row r="4">
@@ -461,19 +461,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2: intermediary unsafe abortion rates</t>
+          <t>2: intermediary induced abortion rates</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3: highest unsafe abortion rates</t>
+          <t>3: highest induced abortion rates</t>
         </is>
       </c>
       <c r="D4">
-        <v>9.6967069373689</v>
+        <v>9.526594368421073</v>
       </c>
       <c r="E4">
-        <v>9.341600130541354E-22</v>
+        <v>4.875828866360225E-21</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>-2.414666601582089</v>
+        <v>-2.381515911713366</v>
       </c>
     </row>
   </sheetData>
